--- a/80_Asset/設計資料/SNFramework.xlsx
+++ b/80_Asset/設計資料/SNFramework.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shinj\OneDrive\ドキュメント\Creation\ソフト開発\SNFramework\80_Asset\設計資料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0424E43B-107F-4D56-9578-72964D5DB172}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{990AA744-6705-4E1C-9FFA-8D48CFA9D47E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="16371" yWindow="0" windowWidth="16629" windowHeight="18600" xr2:uid="{70336C66-D1CA-48C0-83F2-0D9D170A84BC}"/>
   </bookViews>
@@ -17,7 +17,8 @@
     <sheet name="基本方針" sheetId="8" r:id="rId2"/>
     <sheet name="システム構成" sheetId="2" r:id="rId3"/>
     <sheet name="機能一覧" sheetId="33" r:id="rId4"/>
-    <sheet name="てんぷれ" sheetId="5" r:id="rId5"/>
+    <sheet name="スレッド構成" sheetId="34" r:id="rId5"/>
+    <sheet name="てんぷれ" sheetId="5" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="72">
   <si>
     <t>システム構成</t>
     <rPh sb="4" eb="6">
@@ -584,6 +585,197 @@
     </rPh>
     <rPh sb="2" eb="4">
       <t>イチラン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スレッド構成</t>
+    <rPh sb="4" eb="6">
+      <t>コウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>■System</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>■Application</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>■Storage</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>■AudioVideo</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>■Codec</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プライマリ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アプリケーション</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スレッドシーケンサ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ストレージ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サウンド</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ミュージック</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>イメージコーデック</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サウンドコーデック</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スレッド</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>種別</t>
+    <rPh sb="0" eb="2">
+      <t>シュベツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>常駐</t>
+    <rPh sb="0" eb="2">
+      <t>ジョウチュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ワーカー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プログラムのEntryPoint、メインウインドウの制御等</t>
+    <rPh sb="26" eb="28">
+      <t>セイギョ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>ナド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FSP制御、画面UI制御、ゲームロジック実行</t>
+    <rPh sb="3" eb="5">
+      <t>セイギョ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>セイギョ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ジッコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アプリケーションを非同期/分割実行するための仕組み</t>
+    <rPh sb="9" eb="12">
+      <t>ヒドウキ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ブンカツ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ジッコウ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>シク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ストレージアクセスを行う常駐スレッド</t>
+    <rPh sb="10" eb="11">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ジョウチュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メモリ上のPCM再生(SE用途)を行う常駐スレッド</t>
+    <rPh sb="3" eb="4">
+      <t>ジョウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>サイセイ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ヨウト</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ジョウチュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メモリ上のPCMのストリーミング再生(BGM用途)を行うワーカースレッド</t>
+    <rPh sb="3" eb="4">
+      <t>ジョウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>サイセイ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ヨウト</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>PNGのエンコード/デコード処理用の常駐スレッド</t>
+    <rPh sb="14" eb="16">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ヨウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ジョウチュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>MP3のデコード処理用の常駐スレッド</t>
+    <rPh sb="8" eb="11">
+      <t>ショリヨウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ジョウチュウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -664,7 +856,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -724,12 +916,49 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -750,6 +979,9 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
@@ -2399,6 +2631,621 @@
           <a:r>
             <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
             <a:t>WIC</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="正方形/長方形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4E489D77-82BC-4A1E-9647-845DD5FBD72E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5600700" y="702129"/>
+          <a:ext cx="800100" cy="234042"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:schemeClr val="accent5"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent5"/>
+        </a:fillRef>
+        <a:effectRef idx="3">
+          <a:schemeClr val="accent5"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>常駐</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>212270</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="正方形/長方形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9953401C-9D62-8244-FC4A-53A0289C8DFD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6667500" y="680356"/>
+          <a:ext cx="800100" cy="255815"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent6"/>
+        </a:fillRef>
+        <a:effectRef idx="3">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>ワーカー</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="正方形/長方形 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E47FCEB4-A31B-7A3F-55F0-EBFC5766E61E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="533400" y="2106386"/>
+          <a:ext cx="1333500" cy="468086"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:schemeClr val="accent5"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent5"/>
+        </a:fillRef>
+        <a:effectRef idx="3">
+          <a:schemeClr val="accent5"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>プライマリ</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>234042</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="正方形/長方形 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00DD2ED7-13B5-AA81-C12B-91E0C07CB6B4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2133600" y="2106385"/>
+          <a:ext cx="1333500" cy="468086"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:schemeClr val="accent5"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent5"/>
+        </a:fillRef>
+        <a:effectRef idx="3">
+          <a:schemeClr val="accent5"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>アプリケーション</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="正方形/長方形 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FCB15FE4-F7DA-9B31-F5A9-479076D7344A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3733800" y="2106386"/>
+          <a:ext cx="1333500" cy="468086"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:schemeClr val="accent5"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent5"/>
+        </a:fillRef>
+        <a:effectRef idx="3">
+          <a:schemeClr val="accent5"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>ストレージ</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="正方形/長方形 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5D927450-E286-5E21-B76D-0FC3A8854125}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6934200" y="2106386"/>
+          <a:ext cx="1333500" cy="468086"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:schemeClr val="accent5"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent5"/>
+        </a:fillRef>
+        <a:effectRef idx="3">
+          <a:schemeClr val="accent5"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="900"/>
+            <a:t>イメージコーデック</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="正方形/長方形 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{504CCCFB-CB15-FEC1-C658-6C4DE72F01BE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5334000" y="2106386"/>
+          <a:ext cx="1333500" cy="468086"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:schemeClr val="accent5"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent5"/>
+        </a:fillRef>
+        <a:effectRef idx="3">
+          <a:schemeClr val="accent5"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>サウンド</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="正方形/長方形 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F93FEF41-ED1A-90B1-A089-C3CBA12B02B6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2133600" y="2808514"/>
+          <a:ext cx="1333500" cy="468086"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent6"/>
+        </a:fillRef>
+        <a:effectRef idx="3">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="900"/>
+            <a:t>スレッドシーケンサ</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="正方形/長方形 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C4320986-F2C7-5869-6383-563D3BD318A6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6934200" y="2808514"/>
+          <a:ext cx="1333500" cy="468086"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:schemeClr val="accent5"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent5"/>
+        </a:fillRef>
+        <a:effectRef idx="3">
+          <a:schemeClr val="accent5"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="900"/>
+            <a:t>サウンドコーデック</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="正方形/長方形 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CD9837BF-94F7-DBB5-E6B0-821778D4971E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5334000" y="2808514"/>
+          <a:ext cx="1333500" cy="468086"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent6"/>
+        </a:fillRef>
+        <a:effectRef idx="3">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="900"/>
+            <a:t>ミュージック</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -2671,7 +3518,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:B8"/>
+  <dimension ref="B2:B10"/>
   <sheetFormatPr defaultColWidth="3.5" defaultRowHeight="18.45"/>
   <cols>
     <col min="1" max="16384" width="3.5" style="2"/>
@@ -2697,12 +3544,18 @@
         <v>45</v>
       </c>
     </row>
+    <row r="10" spans="2:2">
+      <c r="B10" s="7" t="s">
+        <v>46</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <hyperlinks>
     <hyperlink ref="B4" location="基本方針!A1" display="基本方針" xr:uid="{C3AE92BD-EC43-4AE1-A7E2-DB0302BAFD79}"/>
     <hyperlink ref="B6" location="システム構成!A1" display="システム構成" xr:uid="{4F783A31-E2F8-43CF-AC04-2947764929A0}"/>
     <hyperlink ref="B8" location="機能一覧!A1" display="機能一覧" xr:uid="{EB4BF395-1BCD-43BC-85AB-854F581778C6}"/>
+    <hyperlink ref="B10" location="スレッド構成!A1" display="スレッド構成" xr:uid="{D4467C0E-1895-48E3-87F8-FB58A0F2D9AB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3005,6 +3858,393 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41CAC96B-6693-4587-87EE-136879699F4B}">
+  <dimension ref="A1:AF25"/>
+  <sheetFormatPr defaultColWidth="3.5" defaultRowHeight="18.45"/>
+  <cols>
+    <col min="1" max="16384" width="3.5" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:27">
+      <c r="A1" s="7" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27">
+      <c r="B2" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27">
+      <c r="C9" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="U9" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="AA9" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="17" spans="3:32">
+      <c r="C17" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="13"/>
+      <c r="H17" s="14"/>
+      <c r="I17" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="J17" s="13"/>
+      <c r="K17" s="14"/>
+      <c r="L17" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="M17" s="13"/>
+      <c r="N17" s="13"/>
+      <c r="O17" s="13"/>
+      <c r="P17" s="13"/>
+      <c r="Q17" s="13"/>
+      <c r="R17" s="13"/>
+      <c r="S17" s="13"/>
+      <c r="T17" s="13"/>
+      <c r="U17" s="13"/>
+      <c r="V17" s="13"/>
+      <c r="W17" s="13"/>
+      <c r="X17" s="13"/>
+      <c r="Y17" s="13"/>
+      <c r="Z17" s="13"/>
+      <c r="AA17" s="13"/>
+      <c r="AB17" s="13"/>
+      <c r="AC17" s="13"/>
+      <c r="AD17" s="13"/>
+      <c r="AE17" s="13"/>
+      <c r="AF17" s="14"/>
+    </row>
+    <row r="18" spans="3:32">
+      <c r="C18" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="J18" s="13"/>
+      <c r="K18" s="14"/>
+      <c r="L18" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="M18" s="13"/>
+      <c r="N18" s="13"/>
+      <c r="O18" s="13"/>
+      <c r="P18" s="13"/>
+      <c r="Q18" s="13"/>
+      <c r="R18" s="13"/>
+      <c r="S18" s="13"/>
+      <c r="T18" s="13"/>
+      <c r="U18" s="13"/>
+      <c r="V18" s="13"/>
+      <c r="W18" s="13"/>
+      <c r="X18" s="13"/>
+      <c r="Y18" s="13"/>
+      <c r="Z18" s="13"/>
+      <c r="AA18" s="13"/>
+      <c r="AB18" s="13"/>
+      <c r="AC18" s="13"/>
+      <c r="AD18" s="13"/>
+      <c r="AE18" s="13"/>
+      <c r="AF18" s="14"/>
+    </row>
+    <row r="19" spans="3:32">
+      <c r="C19" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="14"/>
+      <c r="I19" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="J19" s="13"/>
+      <c r="K19" s="14"/>
+      <c r="L19" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="M19" s="13"/>
+      <c r="N19" s="13"/>
+      <c r="O19" s="13"/>
+      <c r="P19" s="13"/>
+      <c r="Q19" s="13"/>
+      <c r="R19" s="13"/>
+      <c r="S19" s="13"/>
+      <c r="T19" s="13"/>
+      <c r="U19" s="13"/>
+      <c r="V19" s="13"/>
+      <c r="W19" s="13"/>
+      <c r="X19" s="13"/>
+      <c r="Y19" s="13"/>
+      <c r="Z19" s="13"/>
+      <c r="AA19" s="13"/>
+      <c r="AB19" s="13"/>
+      <c r="AC19" s="13"/>
+      <c r="AD19" s="13"/>
+      <c r="AE19" s="13"/>
+      <c r="AF19" s="14"/>
+    </row>
+    <row r="20" spans="3:32">
+      <c r="C20" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="13"/>
+      <c r="H20" s="14"/>
+      <c r="I20" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="J20" s="13"/>
+      <c r="K20" s="14"/>
+      <c r="L20" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="M20" s="13"/>
+      <c r="N20" s="13"/>
+      <c r="O20" s="13"/>
+      <c r="P20" s="13"/>
+      <c r="Q20" s="13"/>
+      <c r="R20" s="13"/>
+      <c r="S20" s="13"/>
+      <c r="T20" s="13"/>
+      <c r="U20" s="13"/>
+      <c r="V20" s="13"/>
+      <c r="W20" s="13"/>
+      <c r="X20" s="13"/>
+      <c r="Y20" s="13"/>
+      <c r="Z20" s="13"/>
+      <c r="AA20" s="13"/>
+      <c r="AB20" s="13"/>
+      <c r="AC20" s="13"/>
+      <c r="AD20" s="13"/>
+      <c r="AE20" s="13"/>
+      <c r="AF20" s="14"/>
+    </row>
+    <row r="21" spans="3:32">
+      <c r="C21" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="14"/>
+      <c r="I21" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="J21" s="13"/>
+      <c r="K21" s="14"/>
+      <c r="L21" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="M21" s="13"/>
+      <c r="N21" s="13"/>
+      <c r="O21" s="13"/>
+      <c r="P21" s="13"/>
+      <c r="Q21" s="13"/>
+      <c r="R21" s="13"/>
+      <c r="S21" s="13"/>
+      <c r="T21" s="13"/>
+      <c r="U21" s="13"/>
+      <c r="V21" s="13"/>
+      <c r="W21" s="13"/>
+      <c r="X21" s="13"/>
+      <c r="Y21" s="13"/>
+      <c r="Z21" s="13"/>
+      <c r="AA21" s="13"/>
+      <c r="AB21" s="13"/>
+      <c r="AC21" s="13"/>
+      <c r="AD21" s="13"/>
+      <c r="AE21" s="13"/>
+      <c r="AF21" s="14"/>
+    </row>
+    <row r="22" spans="3:32">
+      <c r="C22" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="13"/>
+      <c r="H22" s="14"/>
+      <c r="I22" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="J22" s="13"/>
+      <c r="K22" s="14"/>
+      <c r="L22" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="M22" s="13"/>
+      <c r="N22" s="13"/>
+      <c r="O22" s="13"/>
+      <c r="P22" s="13"/>
+      <c r="Q22" s="13"/>
+      <c r="R22" s="13"/>
+      <c r="S22" s="13"/>
+      <c r="T22" s="13"/>
+      <c r="U22" s="13"/>
+      <c r="V22" s="13"/>
+      <c r="W22" s="13"/>
+      <c r="X22" s="13"/>
+      <c r="Y22" s="13"/>
+      <c r="Z22" s="13"/>
+      <c r="AA22" s="13"/>
+      <c r="AB22" s="13"/>
+      <c r="AC22" s="13"/>
+      <c r="AD22" s="13"/>
+      <c r="AE22" s="13"/>
+      <c r="AF22" s="14"/>
+    </row>
+    <row r="23" spans="3:32">
+      <c r="C23" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="13"/>
+      <c r="H23" s="14"/>
+      <c r="I23" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="J23" s="13"/>
+      <c r="K23" s="14"/>
+      <c r="L23" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="M23" s="13"/>
+      <c r="N23" s="13"/>
+      <c r="O23" s="13"/>
+      <c r="P23" s="13"/>
+      <c r="Q23" s="13"/>
+      <c r="R23" s="13"/>
+      <c r="S23" s="13"/>
+      <c r="T23" s="13"/>
+      <c r="U23" s="13"/>
+      <c r="V23" s="13"/>
+      <c r="W23" s="13"/>
+      <c r="X23" s="13"/>
+      <c r="Y23" s="13"/>
+      <c r="Z23" s="13"/>
+      <c r="AA23" s="13"/>
+      <c r="AB23" s="13"/>
+      <c r="AC23" s="13"/>
+      <c r="AD23" s="13"/>
+      <c r="AE23" s="13"/>
+      <c r="AF23" s="14"/>
+    </row>
+    <row r="24" spans="3:32">
+      <c r="C24" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="13"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="J24" s="13"/>
+      <c r="K24" s="14"/>
+      <c r="L24" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="M24" s="13"/>
+      <c r="N24" s="13"/>
+      <c r="O24" s="13"/>
+      <c r="P24" s="13"/>
+      <c r="Q24" s="13"/>
+      <c r="R24" s="13"/>
+      <c r="S24" s="13"/>
+      <c r="T24" s="13"/>
+      <c r="U24" s="13"/>
+      <c r="V24" s="13"/>
+      <c r="W24" s="13"/>
+      <c r="X24" s="13"/>
+      <c r="Y24" s="13"/>
+      <c r="Z24" s="13"/>
+      <c r="AA24" s="13"/>
+      <c r="AB24" s="13"/>
+      <c r="AC24" s="13"/>
+      <c r="AD24" s="13"/>
+      <c r="AE24" s="13"/>
+      <c r="AF24" s="14"/>
+    </row>
+    <row r="25" spans="3:32">
+      <c r="C25" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="D25" s="13"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="13"/>
+      <c r="G25" s="13"/>
+      <c r="H25" s="14"/>
+      <c r="I25" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="J25" s="13"/>
+      <c r="K25" s="14"/>
+      <c r="L25" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="M25" s="13"/>
+      <c r="N25" s="13"/>
+      <c r="O25" s="13"/>
+      <c r="P25" s="13"/>
+      <c r="Q25" s="13"/>
+      <c r="R25" s="13"/>
+      <c r="S25" s="13"/>
+      <c r="T25" s="13"/>
+      <c r="U25" s="13"/>
+      <c r="V25" s="13"/>
+      <c r="W25" s="13"/>
+      <c r="X25" s="13"/>
+      <c r="Y25" s="13"/>
+      <c r="Z25" s="13"/>
+      <c r="AA25" s="13"/>
+      <c r="AB25" s="13"/>
+      <c r="AC25" s="13"/>
+      <c r="AD25" s="13"/>
+      <c r="AE25" s="13"/>
+      <c r="AF25" s="14"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="A1" location="目次!A1" display="目次" xr:uid="{D398055C-C831-4758-B4D0-FDB8852231A3}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BE56C44-4667-470E-9226-94958812C4D7}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultColWidth="3.5" defaultRowHeight="18.45"/>

--- a/80_Asset/設計資料/SNFramework.xlsx
+++ b/80_Asset/設計資料/SNFramework.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shinj\OneDrive\ドキュメント\Creation\ソフト開発\SNFramework\80_Asset\設計資料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{990AA744-6705-4E1C-9FFA-8D48CFA9D47E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F1C1C63-64B3-4453-B1D7-9638FDA4EC7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16371" yWindow="0" windowWidth="16629" windowHeight="18600" xr2:uid="{70336C66-D1CA-48C0-83F2-0D9D170A84BC}"/>
+    <workbookView xWindow="-86" yWindow="0" windowWidth="16629" windowHeight="18600" activeTab="5" xr2:uid="{70336C66-D1CA-48C0-83F2-0D9D170A84BC}"/>
   </bookViews>
   <sheets>
     <sheet name="目次" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,8 @@
     <sheet name="システム構成" sheetId="2" r:id="rId3"/>
     <sheet name="機能一覧" sheetId="33" r:id="rId4"/>
     <sheet name="スレッド構成" sheetId="34" r:id="rId5"/>
-    <sheet name="てんぷれ" sheetId="5" r:id="rId6"/>
+    <sheet name="アプリ構成" sheetId="35" r:id="rId6"/>
+    <sheet name="てんぷれ" sheetId="5" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="102">
   <si>
     <t>システム構成</t>
     <rPh sb="4" eb="6">
@@ -777,6 +778,237 @@
     <rPh sb="12" eb="14">
       <t>ジョウチュウ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>World</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゲーム内世界を実現する</t>
+    <rPh sb="3" eb="4">
+      <t>ナイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>セカイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ジツゲン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アプリ構成</t>
+    <rPh sb="3" eb="5">
+      <t>コウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Application配下の構成を示す。</t>
+    <rPh sb="11" eb="13">
+      <t>ハイカ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>コウセイ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>シメ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>以下レイヤから構成する。</t>
+    <rPh sb="0" eb="2">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>コウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DebugApp</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SysApp</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UserApp</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OverlapApp</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BgApp</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デバッグ情報表示など</t>
+    <rPh sb="4" eb="6">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アプリ全体にかかわる制御を行うレイヤ</t>
+    <rPh sb="3" eb="5">
+      <t>ゼンタイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>セイギョ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>システムとして固定のアプリケーション。システム設定等。</t>
+    <rPh sb="7" eb="9">
+      <t>コテイ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ナド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アプリケーション毎に実装するレイヤ。</t>
+    <rPh sb="8" eb="9">
+      <t>ゴト</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ジッソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>どのレイヤでも処理しないイベントを処理するレイヤ。フェールセーフ含む。</t>
+    <rPh sb="7" eb="9">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>フク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SysAppのステートフロー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アプリ実行</t>
+    <rPh sb="3" eb="5">
+      <t>ジッコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>起動完了</t>
+    <rPh sb="0" eb="2">
+      <t>キドウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エラー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リソースロード完了</t>
+    <rPh sb="7" eb="9">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>[システム設定]</t>
+    <rPh sb="5" eb="7">
+      <t>セッテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>[x], [終了]</t>
+    <rPh sb="6" eb="8">
+      <t>シュウリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UserAppのステートフロー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Runはサブステートとして以下のレイヤ構造を持つ</t>
+    <rPh sb="13" eb="15">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>コウゾウ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>モ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メニュー表示を行うレイヤ</t>
+    <rPh sb="4" eb="6">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>WorldApp</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>MenuApp</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ワールドの表示、イベント通知を行うレイヤ</t>
+    <rPh sb="5" eb="7">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ツウチ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>[メニュー表示]</t>
+    <rPh sb="5" eb="7">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>MenuAppのサブステート</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2254,16 +2486,8 @@
           <a:pPr algn="ctr"/>
           <a:r>
             <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
-            <a:t>Game</a:t>
+            <a:t>World</a:t>
           </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
-            <a:t>Object</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -3250,6 +3474,1716 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="7" name="直線矢印コネクタ 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C4FE4B1D-0FD8-51F8-4791-2F9768FA72E2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:endCxn id="8" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1600200" y="4212771"/>
+          <a:ext cx="0" cy="468086"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="dk1"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="oval" w="lg" len="lg"/>
+          <a:tailEnd type="arrow" w="med" len="med"/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+            <a:prstClr val="black">
+              <a:alpha val="40000"/>
+            </a:prstClr>
+          </a:outerShdw>
+        </a:effectLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="四角形: 角を丸くする 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FA4E8611-C8CB-6244-A1AC-6FF90B2D7AD1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1066800" y="4680857"/>
+          <a:ext cx="1066800" cy="468086"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:schemeClr val="accent5"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent5"/>
+        </a:fillRef>
+        <a:effectRef idx="3">
+          <a:schemeClr val="accent5"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>Startup</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="四角形: 角を丸くする 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{872EC324-FBB6-A358-E1CF-666DC484AC12}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1066800" y="5617029"/>
+          <a:ext cx="1066800" cy="468086"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:schemeClr val="accent5"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent5"/>
+        </a:fillRef>
+        <a:effectRef idx="3">
+          <a:schemeClr val="accent5"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>Loading</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="四角形: 角を丸くする 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B5D6738F-04B8-5722-1B86-550BD84C105B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3467100" y="5617029"/>
+          <a:ext cx="1066800" cy="468086"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:schemeClr val="accent5"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent5"/>
+        </a:fillRef>
+        <a:effectRef idx="3">
+          <a:schemeClr val="accent5"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>Error</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="四角形: 角を丸くする 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{492B8CEB-AE5C-850E-0DA7-F47A41A54BE6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1066800" y="6553200"/>
+          <a:ext cx="1066800" cy="468086"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:schemeClr val="accent5"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent5"/>
+        </a:fillRef>
+        <a:effectRef idx="3">
+          <a:schemeClr val="accent5"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>Title</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="16" name="四角形: 角を丸くする 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8DFFB951-E596-9B8B-5CE3-1641BA05A93E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3467100" y="7489371"/>
+          <a:ext cx="1066800" cy="468086"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:schemeClr val="accent5"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent5"/>
+        </a:fillRef>
+        <a:effectRef idx="3">
+          <a:schemeClr val="accent5"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>Config</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="17" name="四角形: 角を丸くする 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C18DFA61-6727-DFAE-B703-E0FE00765D04}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3467100" y="6553200"/>
+          <a:ext cx="1066800" cy="468086"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:schemeClr val="accent5"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent5"/>
+        </a:fillRef>
+        <a:effectRef idx="3">
+          <a:schemeClr val="accent5"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>PreClose</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="18" name="四角形: 角を丸くする 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E61ED114-868E-4FFA-BB30-261D3EBA517C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1066800" y="7489371"/>
+          <a:ext cx="1066800" cy="468086"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:schemeClr val="accent5"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent5"/>
+        </a:fillRef>
+        <a:effectRef idx="3">
+          <a:schemeClr val="accent5"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>Idle</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="19" name="直線矢印コネクタ 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{643B3455-39CF-BEDF-029D-7B75F286870E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="8" idx="2"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1600200" y="5148943"/>
+          <a:ext cx="0" cy="468086"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="dk1"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="none" w="lg" len="lg"/>
+          <a:tailEnd type="arrow" w="med" len="med"/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+            <a:prstClr val="black">
+              <a:alpha val="40000"/>
+            </a:prstClr>
+          </a:outerShdw>
+        </a:effectLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="22" name="直線矢印コネクタ 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{06ADFA1D-F107-6C29-3054-84F1A78654CE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="13" idx="2"/>
+          <a:endCxn id="15" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1600200" y="6085115"/>
+          <a:ext cx="0" cy="468085"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="dk1"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="none" w="lg" len="lg"/>
+          <a:tailEnd type="arrow" w="med" len="med"/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+            <a:prstClr val="black">
+              <a:alpha val="40000"/>
+            </a:prstClr>
+          </a:outerShdw>
+        </a:effectLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="25" name="直線矢印コネクタ 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{91714F88-E024-491E-C091-A3549E6E8AB3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="15" idx="2"/>
+          <a:endCxn id="18" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1600200" y="7021286"/>
+          <a:ext cx="0" cy="468085"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="dk1"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="none" w="lg" len="lg"/>
+          <a:tailEnd type="arrow" w="med" len="med"/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+            <a:prstClr val="black">
+              <a:alpha val="40000"/>
+            </a:prstClr>
+          </a:outerShdw>
+        </a:effectLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="28" name="直線矢印コネクタ 27">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D61BE2F3-2134-3432-4A97-2DE6B027566A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="18" idx="3"/>
+          <a:endCxn id="17" idx="2"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="2133600" y="7021286"/>
+          <a:ext cx="1866900" cy="702128"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="dk1"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="arrow" w="lg" len="lg"/>
+          <a:tailEnd type="arrow" w="med" len="med"/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+            <a:prstClr val="black">
+              <a:alpha val="40000"/>
+            </a:prstClr>
+          </a:outerShdw>
+        </a:effectLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="31" name="直線矢印コネクタ 30">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D0F6C229-0949-821F-63DA-0F95D91D5387}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="18" idx="3"/>
+          <a:endCxn id="16" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2133600" y="7723414"/>
+          <a:ext cx="1333500" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="dk1"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="arrow" w="lg" len="lg"/>
+          <a:tailEnd type="arrow" w="med" len="med"/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+            <a:prstClr val="black">
+              <a:alpha val="40000"/>
+            </a:prstClr>
+          </a:outerShdw>
+        </a:effectLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="34" name="直線矢印コネクタ 33">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8A9B4A04-42BC-CE4A-E83D-C62B5386EF25}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="15" idx="3"/>
+          <a:endCxn id="16" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2133600" y="6787243"/>
+          <a:ext cx="1866900" cy="702128"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="dk1"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="arrow" w="lg" len="lg"/>
+          <a:tailEnd type="arrow" w="med" len="med"/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+            <a:prstClr val="black">
+              <a:alpha val="40000"/>
+            </a:prstClr>
+          </a:outerShdw>
+        </a:effectLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="37" name="直線矢印コネクタ 36">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E2691728-9687-098E-0696-1C275E2EB6E9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="15" idx="3"/>
+          <a:endCxn id="17" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2133600" y="6787243"/>
+          <a:ext cx="1333500" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="dk1"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="arrow" w="lg" len="lg"/>
+          <a:tailEnd type="arrow" w="med" len="med"/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+            <a:prstClr val="black">
+              <a:alpha val="40000"/>
+            </a:prstClr>
+          </a:outerShdw>
+        </a:effectLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="41" name="直線矢印コネクタ 40">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{77A3B631-C7BE-04DE-0885-821619E9355C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="13" idx="3"/>
+          <a:endCxn id="14" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2133600" y="5851072"/>
+          <a:ext cx="1333500" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="dk1"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="none" w="lg" len="lg"/>
+          <a:tailEnd type="arrow" w="med" len="med"/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+            <a:prstClr val="black">
+              <a:alpha val="40000"/>
+            </a:prstClr>
+          </a:outerShdw>
+        </a:effectLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="50" name="四角形: 角を丸くする 49">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0927A081-627F-3863-57B0-02F2AABF9B20}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1066800" y="9127671"/>
+          <a:ext cx="1066800" cy="468086"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:schemeClr val="accent5"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent5"/>
+        </a:fillRef>
+        <a:effectRef idx="3">
+          <a:schemeClr val="accent5"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>Off</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="51" name="直線矢印コネクタ 50">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D2DF2A36-D622-0078-0A45-8E202B493E4F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:endCxn id="50" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1600200" y="8659586"/>
+          <a:ext cx="0" cy="468085"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="dk1"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="oval" w="lg" len="lg"/>
+          <a:tailEnd type="arrow" w="med" len="med"/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+            <a:prstClr val="black">
+              <a:alpha val="40000"/>
+            </a:prstClr>
+          </a:outerShdw>
+        </a:effectLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="55" name="四角形: 角を丸くする 54">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DDCC580A-7BC6-E3DD-0C6B-CB0CDE9841C3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1066800" y="10063843"/>
+          <a:ext cx="1066800" cy="468086"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:schemeClr val="accent5"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent5"/>
+        </a:fillRef>
+        <a:effectRef idx="3">
+          <a:schemeClr val="accent5"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>Title</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="56" name="直線矢印コネクタ 55">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{17CE058D-2D8B-731F-B1BA-CFEC8ADBC28E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="50" idx="2"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1600200" y="9595757"/>
+          <a:ext cx="0" cy="468086"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="dk1"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="none" w="lg" len="lg"/>
+          <a:tailEnd type="arrow" w="med" len="med"/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+            <a:prstClr val="black">
+              <a:alpha val="40000"/>
+            </a:prstClr>
+          </a:outerShdw>
+        </a:effectLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="59" name="四角形: 角を丸くする 58">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7F148879-7064-38CB-472D-AD03EE965B80}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1066800" y="11000014"/>
+          <a:ext cx="1066800" cy="468086"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:schemeClr val="accent5"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent5"/>
+        </a:fillRef>
+        <a:effectRef idx="3">
+          <a:schemeClr val="accent5"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>Run</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="60" name="直線矢印コネクタ 59">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7DF8F7FC-B76A-6297-7E74-3562E44B0AB7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="55" idx="2"/>
+          <a:endCxn id="59" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1600200" y="10531929"/>
+          <a:ext cx="0" cy="468085"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="dk1"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="none" w="lg" len="lg"/>
+          <a:tailEnd type="arrow" w="med" len="med"/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+            <a:prstClr val="black">
+              <a:alpha val="40000"/>
+            </a:prstClr>
+          </a:outerShdw>
+        </a:effectLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="70" name="四角形: 角を丸くする 69">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C646C6E1-CD9C-C03B-D99A-3B3DCC1672B1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1066800" y="14510657"/>
+          <a:ext cx="1066800" cy="468086"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:schemeClr val="accent5"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent5"/>
+        </a:fillRef>
+        <a:effectRef idx="3">
+          <a:schemeClr val="accent5"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>MenuOff</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="71" name="直線矢印コネクタ 70">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{45659A25-1E81-CF54-ED65-A853466291B5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:endCxn id="70" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1600200" y="14042571"/>
+          <a:ext cx="0" cy="468086"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="dk1"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="oval" w="lg" len="lg"/>
+          <a:tailEnd type="arrow" w="med" len="med"/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+            <a:prstClr val="black">
+              <a:alpha val="40000"/>
+            </a:prstClr>
+          </a:outerShdw>
+        </a:effectLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="74" name="四角形: 角を丸くする 73">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E0A5A921-D30F-4B57-05BC-E825F52326E5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1066800" y="15680871"/>
+          <a:ext cx="1066800" cy="468086"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:schemeClr val="accent5"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent5"/>
+        </a:fillRef>
+        <a:effectRef idx="3">
+          <a:schemeClr val="accent5"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>MainMenu</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="77" name="直線矢印コネクタ 76">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FA16CA5D-3A47-7129-152B-DEEE2E0E915F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="74" idx="0"/>
+          <a:endCxn id="70" idx="2"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="1600200" y="14978743"/>
+          <a:ext cx="0" cy="702128"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="dk1"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="arrow" w="lg" len="lg"/>
+          <a:tailEnd type="arrow" w="med" len="med"/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+            <a:prstClr val="black">
+              <a:alpha val="40000"/>
+            </a:prstClr>
+          </a:outerShdw>
+        </a:effectLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -3606,7 +5540,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="69.45" customHeight="1">
+    <row r="7" spans="1:4" ht="69.55" customHeight="1">
       <c r="C7" s="8">
         <v>3</v>
       </c>
@@ -3677,12 +5611,12 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D171D681-A9A5-4CE8-81C1-2122DDCC5DF0}">
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr defaultColWidth="3.5" defaultRowHeight="18.45"/>
   <cols>
     <col min="1" max="1" width="3.5" style="2"/>
     <col min="2" max="2" width="20.0703125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="52.28515625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="52.2109375" style="2" customWidth="1"/>
     <col min="4" max="16384" width="3.5" style="2"/>
   </cols>
   <sheetData>
@@ -3846,6 +5780,14 @@
       <c r="B25" s="6"/>
       <c r="C25" s="3" t="s">
         <v>42</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3">
+      <c r="B26" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -4245,6 +6187,165 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9B70F55-56A6-4FD5-8899-0A0BC39BAAEF}">
+  <dimension ref="A1:J66"/>
+  <sheetFormatPr defaultColWidth="3.5" defaultRowHeight="18.45"/>
+  <cols>
+    <col min="1" max="16384" width="3.5" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="7" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="B2" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="C4" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="C6" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="D8" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="D9" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="D10" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="D11" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="D12" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="C16" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="18" spans="7:10">
+      <c r="G18" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="22" spans="7:10">
+      <c r="G22" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="24" spans="7:10">
+      <c r="I24" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="26" spans="7:10">
+      <c r="G26" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="28" spans="7:10">
+      <c r="J28" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="33" spans="3:10">
+      <c r="J33" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="36" spans="3:10">
+      <c r="C36" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="38" spans="3:10">
+      <c r="G38" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="42" spans="3:10">
+      <c r="G42" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="53" spans="3:8">
+      <c r="C53" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="55" spans="3:8">
+      <c r="D55" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="56" spans="3:8">
+      <c r="D56" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="59" spans="3:8">
+      <c r="C59" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="66" spans="7:7">
+      <c r="G66" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="A1" location="目次!A1" display="目次" xr:uid="{A5FDA511-E4D1-4762-B0FD-EBC97ACD6BD1}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BE56C44-4667-470E-9226-94958812C4D7}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultColWidth="3.5" defaultRowHeight="18.45"/>
